--- a/public/template/form_upload_luwina.xlsx
+++ b/public/template/form_upload_luwina.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>NAMA PROJECT:</t>
   </si>
@@ -53,7 +53,16 @@
     <t>* Penulisan Designator harap menggunakan huruf kapital</t>
   </si>
   <si>
+    <t>* Penulisan Harga harap menggunakan format "General"</t>
+  </si>
+  <si>
     <t>DESIGNATOR</t>
+  </si>
+  <si>
+    <t>HARGA MATERIAL</t>
+  </si>
+  <si>
+    <t>HARGA JASA</t>
   </si>
   <si>
     <t>VOLUME</t>
@@ -1269,6 +1278,8 @@
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="20.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="17.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="17.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1307,21 +1318,36 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:4">
       <c r="A8" s="3"/>
       <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A7:A8">
